--- a/weekly_stock_tracker_manual.xlsx
+++ b/weekly_stock_tracker_manual.xlsx
@@ -9,15 +9,13 @@
   <sheets>
     <sheet name="Stock Data" sheetId="1" r:id="rId1"/>
     <sheet name="Decision Journal" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="30">
   <si>
     <t>Week Start</t>
   </si>
@@ -67,9 +65,6 @@
     <t>NVDA</t>
   </si>
   <si>
-    <t>NVDA(Est.)</t>
-  </si>
-  <si>
     <t>Alphabet</t>
   </si>
   <si>
@@ -82,12 +77,6 @@
     <t>META</t>
   </si>
   <si>
-    <t>GOOGL(Est.)</t>
-  </si>
-  <si>
-    <t>META(Est.)</t>
-  </si>
-  <si>
     <t>Date</t>
   </si>
   <si>
@@ -113,12 +102,6 @@
   </si>
   <si>
     <t>Notes/Lesson</t>
-  </si>
-  <si>
-    <t>AAPL(Est.)</t>
-  </si>
-  <si>
-    <t>MSFT(Est.)</t>
   </si>
   <si>
     <t>WATCH LIST</t>
@@ -134,7 +117,7 @@
     <numFmt numFmtId="166" formatCode="[Color3]\+0.0%;[Color10]\ \-0.0%;&quot;0.0%&quot;"/>
     <numFmt numFmtId="167" formatCode="[Color10]\+0.0%;[Color3]\ \-0.0%;&quot;0.0%&quot;"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -161,6 +144,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF74B230"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -251,13 +241,123 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="18">
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="6" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="6" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="6" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="6" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="6" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="6" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="6" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="6" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="6" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="6" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="6" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF74B230"/>
+    </mruColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -546,7 +646,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:P36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -609,13 +709,13 @@
         <v>416.67</v>
       </c>
       <c r="G2" s="8">
-        <f t="shared" ref="G2:G31" si="0">(F2-E2)/E2</f>
+        <f t="shared" ref="G2:G36" si="0">(F2-E2)/E2</f>
         <v>-9.5218448710153669E-2</v>
       </c>
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
       <c r="J2" s="5" t="str">
-        <f t="shared" ref="J2:J31" si="1">IF(F2&gt;E2,"UP","DOWN")</f>
+        <f t="shared" ref="J2:J36" si="1">IF(F2&gt;E2,"UP","DOWN")</f>
         <v>DOWN</v>
       </c>
     </row>
@@ -710,7 +810,7 @@
         <v>381.03666666666669</v>
       </c>
       <c r="I5" s="12"/>
-      <c r="J5" s="10" t="str">
+      <c r="J5" s="23" t="str">
         <f t="shared" si="1"/>
         <v>UP</v>
       </c>
@@ -755,76 +855,68 @@
       <c r="A7" s="9">
         <v>46209</v>
       </c>
-      <c r="B7" s="23">
-        <v>46216</v>
+      <c r="B7" s="9">
+        <v>46213</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="E7" s="11">
-        <f>F6</f>
-        <v>390.49</v>
+        <v>391</v>
       </c>
       <c r="F7" s="12">
-        <f>F6+AVERAGE(F3-F2,F4-F3,F5-F4)</f>
-        <v>375.92333333333335</v>
+        <v>395.2</v>
       </c>
       <c r="G7" s="13">
         <f t="shared" si="0"/>
-        <v>-3.7303558776579843E-2</v>
+        <v>1.0741687979539612E-2</v>
       </c>
       <c r="H7" s="12">
         <f>AVERAGE(F5:F7)</f>
-        <v>379.79444444444448</v>
+        <v>386.22</v>
       </c>
       <c r="I7" s="15">
         <f>AVERAGE(F3:F7)</f>
-        <v>381.90466666666669</v>
+        <v>385.76000000000005</v>
       </c>
       <c r="J7" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>DOWN</v>
+        <v>UP</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="4">
-        <v>46174</v>
+        <v>46216</v>
       </c>
       <c r="B8" s="4">
-        <v>46178</v>
+        <v>46220</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E8" s="6">
-        <v>306.31</v>
+        <v>396.1</v>
       </c>
       <c r="F8" s="7">
-        <v>307.33999999999997</v>
-      </c>
-      <c r="G8" s="8">
-        <f t="shared" si="0"/>
-        <v>3.3626065097449405E-3</v>
-      </c>
+        <v>401.15</v>
+      </c>
+      <c r="G8" s="8"/>
       <c r="H8" s="7"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>UP</v>
-      </c>
+      <c r="I8" s="14"/>
+      <c r="J8" s="5"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="9">
-        <v>46181</v>
+        <v>46174</v>
       </c>
       <c r="B9" s="9">
-        <v>46185</v>
+        <v>46178</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>12</v>
@@ -833,28 +925,28 @@
         <v>13</v>
       </c>
       <c r="E9" s="11">
-        <v>301.54000000000002</v>
+        <v>306.31</v>
       </c>
       <c r="F9" s="12">
-        <v>291.13</v>
+        <v>307.33999999999997</v>
       </c>
       <c r="G9" s="13">
         <f t="shared" si="0"/>
-        <v>-3.452278304702535E-2</v>
-      </c>
-      <c r="H9" s="10"/>
+        <v>3.3626065097449405E-3</v>
+      </c>
+      <c r="H9" s="12"/>
       <c r="I9" s="10"/>
       <c r="J9" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>DOWN</v>
+        <v>UP</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="4">
-        <v>46188</v>
+        <v>46181</v>
       </c>
       <c r="B10" s="4">
-        <v>46191</v>
+        <v>46185</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>12</v>
@@ -863,31 +955,28 @@
         <v>13</v>
       </c>
       <c r="E10" s="6">
-        <v>296.42</v>
+        <v>301.54000000000002</v>
       </c>
       <c r="F10" s="7">
-        <v>298.01</v>
+        <v>291.13</v>
       </c>
       <c r="G10" s="8">
         <f t="shared" si="0"/>
-        <v>5.3640105256054747E-3</v>
-      </c>
-      <c r="H10" s="7">
-        <f>AVERAGE(F8:F10)</f>
-        <v>298.82666666666665</v>
-      </c>
+        <v>-3.452278304702535E-2</v>
+      </c>
+      <c r="H10" s="5"/>
       <c r="I10" s="5"/>
       <c r="J10" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>UP</v>
+        <v>DOWN</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="9">
-        <v>46195</v>
+        <v>46188</v>
       </c>
       <c r="B11" s="9">
-        <v>46199</v>
+        <v>46191</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>12</v>
@@ -896,31 +985,31 @@
         <v>13</v>
       </c>
       <c r="E11" s="11">
-        <v>297.01</v>
+        <v>296.42</v>
       </c>
       <c r="F11" s="12">
-        <v>283.77999999999997</v>
+        <v>298.01</v>
       </c>
       <c r="G11" s="13">
         <f t="shared" si="0"/>
-        <v>-4.4543954748998416E-2</v>
+        <v>5.3640105256054747E-3</v>
       </c>
       <c r="H11" s="12">
         <f>AVERAGE(F9:F11)</f>
-        <v>290.9733333333333</v>
+        <v>298.82666666666665</v>
       </c>
       <c r="I11" s="10"/>
       <c r="J11" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>DOWN</v>
+        <v>UP</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="4">
-        <v>46202</v>
+        <v>46195</v>
       </c>
       <c r="B12" s="4">
-        <v>46206</v>
+        <v>46199</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>12</v>
@@ -929,132 +1018,139 @@
         <v>13</v>
       </c>
       <c r="E12" s="6">
-        <v>281.74</v>
+        <v>297.01</v>
       </c>
       <c r="F12" s="7">
-        <v>308.63</v>
+        <v>283.77999999999997</v>
       </c>
       <c r="G12" s="8">
         <f t="shared" si="0"/>
-        <v>9.5442606658621379E-2</v>
+        <v>-4.4543954748998416E-2</v>
       </c>
       <c r="H12" s="7">
         <f>AVERAGE(F10:F12)</f>
-        <v>296.80666666666667</v>
-      </c>
-      <c r="I12" s="14">
-        <f>AVERAGE(F8:F12)</f>
-        <v>297.77799999999996</v>
-      </c>
+        <v>290.9733333333333</v>
+      </c>
+      <c r="I12" s="5"/>
       <c r="J12" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>UP</v>
+        <v>DOWN</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="9">
-        <v>46209</v>
-      </c>
-      <c r="B13" s="23">
-        <v>46216</v>
+        <v>46202</v>
+      </c>
+      <c r="B13" s="9">
+        <v>46206</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>12</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="E13" s="11">
-        <f>F12</f>
+        <v>281.74</v>
+      </c>
+      <c r="F13" s="12">
         <v>308.63</v>
       </c>
-      <c r="F13" s="12">
-        <f>F12+AVERAGE(F9-F8,F10-F9,F11-F10)</f>
-        <v>300.77666666666664</v>
-      </c>
       <c r="G13" s="13">
         <f t="shared" si="0"/>
-        <v>-2.544578729654717E-2</v>
+        <v>9.5442606658621379E-2</v>
       </c>
       <c r="H13" s="12">
         <f>AVERAGE(F11:F13)</f>
-        <v>297.72888888888889</v>
+        <v>296.80666666666667</v>
       </c>
       <c r="I13" s="15">
         <f>AVERAGE(F9:F13)</f>
-        <v>296.46533333333332</v>
+        <v>297.77799999999996</v>
       </c>
       <c r="J13" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>DOWN</v>
+        <v>UP</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="4">
-        <v>46174</v>
+        <v>46209</v>
       </c>
       <c r="B14" s="4">
-        <v>46178</v>
+        <v>46213</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E14" s="6">
-        <v>224.36</v>
+        <v>309.10000000000002</v>
       </c>
       <c r="F14" s="7">
-        <v>205.1</v>
+        <v>312.39999999999998</v>
       </c>
       <c r="G14" s="8">
         <f t="shared" si="0"/>
-        <v>-8.584417899803895E-2</v>
-      </c>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
+        <v>1.0676156583629746E-2</v>
+      </c>
+      <c r="H14" s="7">
+        <f>AVERAGE(F12:F14)</f>
+        <v>301.6033333333333</v>
+      </c>
+      <c r="I14" s="14">
+        <f>AVERAGE(F10:F14)</f>
+        <v>298.78999999999996</v>
+      </c>
       <c r="J14" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>DOWN</v>
+        <v>UP</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="9">
-        <v>46181</v>
+        <v>46216</v>
       </c>
       <c r="B15" s="9">
-        <v>46185</v>
+        <v>46220</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E15" s="11">
-        <v>208.64</v>
+        <v>313</v>
       </c>
       <c r="F15" s="12">
-        <v>205.19</v>
+        <v>315</v>
       </c>
       <c r="G15" s="13">
         <f t="shared" si="0"/>
-        <v>-1.65356595092024E-2</v>
-      </c>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
+        <v>6.3897763578274758E-3</v>
+      </c>
+      <c r="H15" s="12">
+        <f>AVERAGE(F13:F15)</f>
+        <v>312.01</v>
+      </c>
+      <c r="I15" s="15">
+        <f>AVERAGE(F11:F15)</f>
+        <v>303.56399999999996</v>
+      </c>
       <c r="J15" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>DOWN</v>
+        <v>UP</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="4">
-        <v>46188</v>
+        <v>46174</v>
       </c>
       <c r="B16" s="4">
-        <v>46191</v>
+        <v>46178</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>14</v>
@@ -1063,19 +1159,16 @@
         <v>15</v>
       </c>
       <c r="E16" s="6">
-        <v>212.45</v>
+        <v>224.36</v>
       </c>
       <c r="F16" s="7">
-        <v>210.69</v>
+        <v>205.1</v>
       </c>
       <c r="G16" s="8">
         <f t="shared" si="0"/>
-        <v>-8.2843021887502519E-3</v>
-      </c>
-      <c r="H16" s="7">
-        <f>AVERAGE(F14:F16)</f>
-        <v>206.99333333333334</v>
-      </c>
+        <v>-8.584417899803895E-2</v>
+      </c>
+      <c r="H16" s="5"/>
       <c r="I16" s="5"/>
       <c r="J16" s="5" t="str">
         <f t="shared" si="1"/>
@@ -1084,10 +1177,10 @@
     </row>
     <row r="17" spans="1:16">
       <c r="A17" s="9">
-        <v>46195</v>
+        <v>46181</v>
       </c>
       <c r="B17" s="9">
-        <v>46199</v>
+        <v>46185</v>
       </c>
       <c r="C17" s="10" t="s">
         <v>14</v>
@@ -1096,19 +1189,16 @@
         <v>15</v>
       </c>
       <c r="E17" s="11">
-        <v>208.65</v>
+        <v>208.64</v>
       </c>
       <c r="F17" s="12">
-        <v>192.53</v>
+        <v>205.19</v>
       </c>
       <c r="G17" s="13">
         <f t="shared" si="0"/>
-        <v>-7.7258566978193166E-2</v>
-      </c>
-      <c r="H17" s="12">
-        <f>AVERAGE(F15:F17)</f>
-        <v>202.80333333333331</v>
-      </c>
+        <v>-1.65356595092024E-2</v>
+      </c>
+      <c r="H17" s="10"/>
       <c r="I17" s="10"/>
       <c r="J17" s="10" t="str">
         <f t="shared" si="1"/>
@@ -1117,10 +1207,10 @@
     </row>
     <row r="18" spans="1:16">
       <c r="A18" s="4">
-        <v>46202</v>
+        <v>46188</v>
       </c>
       <c r="B18" s="4">
-        <v>46206</v>
+        <v>46191</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>14</v>
@@ -1129,23 +1219,20 @@
         <v>15</v>
       </c>
       <c r="E18" s="6">
-        <v>194.97</v>
+        <v>212.45</v>
       </c>
       <c r="F18" s="7">
-        <v>194.83</v>
+        <v>210.69</v>
       </c>
       <c r="G18" s="8">
         <f t="shared" si="0"/>
-        <v>-7.1805918859304695E-4</v>
+        <v>-8.2843021887502519E-3</v>
       </c>
       <c r="H18" s="7">
         <f>AVERAGE(F16:F18)</f>
-        <v>199.35000000000002</v>
-      </c>
-      <c r="I18" s="14">
-        <f>AVERAGE(F14:F18)</f>
-        <v>201.66800000000001</v>
-      </c>
+        <v>206.99333333333334</v>
+      </c>
+      <c r="I18" s="5"/>
       <c r="J18" s="5" t="str">
         <f t="shared" si="1"/>
         <v>DOWN</v>
@@ -1153,37 +1240,32 @@
     </row>
     <row r="19" spans="1:16">
       <c r="A19" s="9">
-        <v>46209</v>
+        <v>46195</v>
       </c>
       <c r="B19" s="9">
-        <v>46216</v>
+        <v>46199</v>
       </c>
       <c r="C19" s="10" t="s">
         <v>14</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E19" s="11">
-        <f>+F18</f>
-        <v>194.83</v>
+        <v>208.65</v>
       </c>
       <c r="F19" s="12">
-        <f>F18+AVERAGE(F15-F14,F16-F15,F17-F16)</f>
-        <v>190.64000000000001</v>
+        <v>192.53</v>
       </c>
       <c r="G19" s="13">
         <f t="shared" si="0"/>
-        <v>-2.1505928245136773E-2</v>
+        <v>-7.7258566978193166E-2</v>
       </c>
       <c r="H19" s="12">
         <f>AVERAGE(F17:F19)</f>
-        <v>192.66666666666666</v>
-      </c>
-      <c r="I19" s="15">
-        <f>AVERAGE(F15:F19)</f>
-        <v>198.77600000000001</v>
-      </c>
+        <v>202.80333333333331</v>
+      </c>
+      <c r="I19" s="10"/>
       <c r="J19" s="10" t="str">
         <f t="shared" si="1"/>
         <v>DOWN</v>
@@ -1191,29 +1273,35 @@
     </row>
     <row r="20" spans="1:16">
       <c r="A20" s="4">
-        <v>46174</v>
+        <v>46202</v>
       </c>
       <c r="B20" s="4">
-        <v>46178</v>
+        <v>46206</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E20" s="6">
-        <v>376.37</v>
+        <v>194.97</v>
       </c>
       <c r="F20" s="7">
-        <v>368.53</v>
+        <v>194.83</v>
       </c>
       <c r="G20" s="8">
         <f t="shared" si="0"/>
-        <v>-2.0830565666764174E-2</v>
-      </c>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
+        <v>-7.1805918859304695E-4</v>
+      </c>
+      <c r="H20" s="7">
+        <f>AVERAGE(F18:F20)</f>
+        <v>199.35000000000002</v>
+      </c>
+      <c r="I20" s="14">
+        <f>AVERAGE(F16:F20)</f>
+        <v>201.66800000000001</v>
+      </c>
       <c r="J20" s="5" t="str">
         <f t="shared" si="1"/>
         <v>DOWN</v>
@@ -1221,29 +1309,35 @@
     </row>
     <row r="21" spans="1:16">
       <c r="A21" s="9">
-        <v>46181</v>
+        <v>46209</v>
       </c>
       <c r="B21" s="9">
-        <v>46185</v>
+        <v>46213</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E21" s="11">
-        <v>363.31</v>
+        <v>194.5</v>
       </c>
       <c r="F21" s="12">
-        <v>359.68</v>
+        <v>190.1</v>
       </c>
       <c r="G21" s="13">
         <f t="shared" si="0"/>
-        <v>-9.9914673419393783E-3</v>
-      </c>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
+        <v>-2.2622107969151699E-2</v>
+      </c>
+      <c r="H21" s="12">
+        <f>AVERAGE(F19:F21)</f>
+        <v>192.48666666666668</v>
+      </c>
+      <c r="I21" s="15">
+        <f>AVERAGE(F17:F21)</f>
+        <v>198.66800000000001</v>
+      </c>
       <c r="J21" s="10" t="str">
         <f t="shared" si="1"/>
         <v>DOWN</v>
@@ -1251,32 +1345,35 @@
     </row>
     <row r="22" spans="1:16">
       <c r="A22" s="4">
-        <v>46188</v>
+        <v>46216</v>
       </c>
       <c r="B22" s="4">
-        <v>46191</v>
+        <v>46220</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E22" s="6">
-        <v>369.35</v>
+        <v>189.5</v>
       </c>
       <c r="F22" s="7">
-        <v>368.03</v>
+        <v>186.5</v>
       </c>
       <c r="G22" s="8">
         <f t="shared" si="0"/>
-        <v>-3.5738459455802083E-3</v>
+        <v>-1.5831134564643801E-2</v>
       </c>
       <c r="H22" s="7">
         <f>AVERAGE(F20:F22)</f>
-        <v>365.41333333333336</v>
-      </c>
-      <c r="I22" s="5"/>
+        <v>190.47666666666669</v>
+      </c>
+      <c r="I22" s="14">
+        <f>AVERAGE(F18:F22)</f>
+        <v>194.93</v>
+      </c>
       <c r="J22" s="5" t="str">
         <f t="shared" si="1"/>
         <v>DOWN</v>
@@ -1284,31 +1381,28 @@
     </row>
     <row r="23" spans="1:16">
       <c r="A23" s="9">
-        <v>46195</v>
+        <v>46174</v>
       </c>
       <c r="B23" s="9">
-        <v>46199</v>
+        <v>46178</v>
       </c>
       <c r="C23" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D23" s="10" t="s">
-        <v>18</v>
-      </c>
       <c r="E23" s="11">
-        <v>349.68</v>
+        <v>376.37</v>
       </c>
       <c r="F23" s="12">
-        <v>337.39</v>
+        <v>368.53</v>
       </c>
       <c r="G23" s="13">
         <f t="shared" si="0"/>
-        <v>-3.5146419583619366E-2</v>
-      </c>
-      <c r="H23" s="12">
-        <f>AVERAGE(F21:F23)</f>
-        <v>355.0333333333333</v>
-      </c>
+        <v>-2.0830565666764174E-2</v>
+      </c>
+      <c r="H23" s="10"/>
       <c r="I23" s="10"/>
       <c r="J23" s="10" t="str">
         <f t="shared" si="1"/>
@@ -1317,73 +1411,62 @@
     </row>
     <row r="24" spans="1:16">
       <c r="A24" s="4">
-        <v>46202</v>
+        <v>46181</v>
       </c>
       <c r="B24" s="4">
-        <v>46206</v>
+        <v>46185</v>
       </c>
       <c r="C24" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D24" s="5" t="s">
-        <v>18</v>
-      </c>
       <c r="E24" s="6">
-        <v>353.65</v>
+        <v>363.31</v>
       </c>
       <c r="F24" s="7">
-        <v>359.91</v>
+        <v>359.68</v>
       </c>
       <c r="G24" s="8">
         <f t="shared" si="0"/>
-        <v>1.7701116923512082E-2</v>
-      </c>
-      <c r="H24" s="7">
-        <f>AVERAGE(F22:F24)</f>
-        <v>355.10999999999996</v>
-      </c>
-      <c r="I24" s="14">
-        <f>AVERAGE(F20:F24)</f>
-        <v>358.70800000000003</v>
-      </c>
+        <v>-9.9914673419393783E-3</v>
+      </c>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
       <c r="J24" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>UP</v>
+        <v>DOWN</v>
       </c>
     </row>
     <row r="25" spans="1:16">
       <c r="A25" s="9">
-        <v>46209</v>
+        <v>46188</v>
       </c>
       <c r="B25" s="9">
-        <v>46216</v>
+        <v>46191</v>
       </c>
       <c r="C25" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="10" t="s">
-        <v>21</v>
-      </c>
       <c r="E25" s="11">
-        <f>F24</f>
-        <v>359.91</v>
+        <v>369.35</v>
       </c>
       <c r="F25" s="12">
-        <f>F24+AVERAGE(F21-F20,F22-F21,F23-F22)</f>
-        <v>349.53000000000003</v>
+        <v>368.03</v>
       </c>
       <c r="G25" s="13">
         <f t="shared" si="0"/>
-        <v>-2.8840543469200619E-2</v>
+        <v>-3.5738459455802083E-3</v>
       </c>
       <c r="H25" s="12">
         <f>AVERAGE(F23:F25)</f>
-        <v>348.94333333333333</v>
-      </c>
-      <c r="I25" s="15">
-        <f>AVERAGE(F21:F25)</f>
-        <v>354.90800000000002</v>
-      </c>
+        <v>365.41333333333336</v>
+      </c>
+      <c r="I25" s="10"/>
       <c r="J25" s="10" t="str">
         <f t="shared" si="1"/>
         <v>DOWN</v>
@@ -1391,28 +1474,31 @@
     </row>
     <row r="26" spans="1:16">
       <c r="A26" s="4">
-        <v>46174</v>
+        <v>46195</v>
       </c>
       <c r="B26" s="4">
-        <v>46178</v>
+        <v>46199</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E26" s="6">
-        <v>600.47</v>
+        <v>349.68</v>
       </c>
       <c r="F26" s="7">
-        <v>593</v>
+        <v>337.39</v>
       </c>
       <c r="G26" s="8">
         <f t="shared" si="0"/>
-        <v>-1.2440255133478819E-2</v>
-      </c>
-      <c r="H26" s="5"/>
+        <v>-3.5146419583619366E-2</v>
+      </c>
+      <c r="H26" s="7">
+        <f>AVERAGE(F24:F26)</f>
+        <v>355.0333333333333</v>
+      </c>
       <c r="I26" s="5"/>
       <c r="J26" s="5" t="str">
         <f t="shared" si="1"/>
@@ -1421,96 +1507,107 @@
     </row>
     <row r="27" spans="1:16">
       <c r="A27" s="9">
-        <v>46181</v>
+        <v>46202</v>
       </c>
       <c r="B27" s="9">
-        <v>46185</v>
+        <v>46206</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E27" s="11">
-        <v>585.39</v>
+        <v>353.65</v>
       </c>
       <c r="F27" s="12">
-        <v>566.98</v>
+        <v>359.91</v>
       </c>
       <c r="G27" s="13">
         <f t="shared" si="0"/>
-        <v>-3.1449119390491755E-2</v>
-      </c>
-      <c r="H27" s="10"/>
-      <c r="I27" s="10"/>
+        <v>1.7701116923512082E-2</v>
+      </c>
+      <c r="H27" s="12">
+        <f>AVERAGE(F25:F27)</f>
+        <v>355.10999999999996</v>
+      </c>
+      <c r="I27" s="15">
+        <f>AVERAGE(F23:F27)</f>
+        <v>358.70800000000003</v>
+      </c>
       <c r="J27" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>DOWN</v>
+        <v>UP</v>
       </c>
     </row>
     <row r="28" spans="1:16">
       <c r="A28" s="4">
-        <v>46188</v>
+        <v>46209</v>
       </c>
       <c r="B28" s="4">
-        <v>46191</v>
+        <v>46213</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E28" s="6">
-        <v>593.48</v>
+        <v>360.5</v>
       </c>
       <c r="F28" s="7">
-        <v>577.22</v>
+        <v>362.5</v>
       </c>
       <c r="G28" s="8">
         <f t="shared" si="0"/>
-        <v>-2.7397721911437606E-2</v>
+        <v>5.5478502080443829E-3</v>
       </c>
       <c r="H28" s="7">
         <f>AVERAGE(F26:F28)</f>
-        <v>579.06666666666672</v>
-      </c>
-      <c r="I28" s="5"/>
+        <v>353.26666666666665</v>
+      </c>
+      <c r="I28" s="14">
+        <f>AVERAGE(F24:F28)</f>
+        <v>357.50200000000001</v>
+      </c>
       <c r="J28" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>DOWN</v>
-      </c>
-      <c r="P28" s="3"/>
+        <v>UP</v>
+      </c>
     </row>
     <row r="29" spans="1:16">
       <c r="A29" s="9">
-        <v>46195</v>
+        <v>46216</v>
       </c>
       <c r="B29" s="9">
-        <v>46199</v>
+        <v>46220</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E29" s="11">
-        <v>563.85</v>
+        <v>363</v>
       </c>
       <c r="F29" s="12">
-        <v>550.25</v>
+        <v>360</v>
       </c>
       <c r="G29" s="13">
         <f t="shared" si="0"/>
-        <v>-2.4119890041677791E-2</v>
+        <v>-8.2644628099173556E-3</v>
       </c>
       <c r="H29" s="12">
         <f>AVERAGE(F27:F29)</f>
-        <v>564.81666666666672</v>
-      </c>
-      <c r="I29" s="10"/>
+        <v>360.80333333333334</v>
+      </c>
+      <c r="I29" s="15">
+        <f>AVERAGE(F25:F29)</f>
+        <v>357.56599999999997</v>
+      </c>
       <c r="J29" s="10" t="str">
         <f t="shared" si="1"/>
         <v>DOWN</v>
@@ -1518,79 +1615,251 @@
     </row>
     <row r="30" spans="1:16">
       <c r="A30" s="4">
-        <v>46202</v>
+        <v>46174</v>
       </c>
       <c r="B30" s="4">
-        <v>46206</v>
+        <v>46178</v>
       </c>
       <c r="C30" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D30" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D30" s="5" t="s">
-        <v>20</v>
-      </c>
       <c r="E30" s="6">
-        <v>562.6</v>
+        <v>600.47</v>
       </c>
       <c r="F30" s="7">
-        <v>582.9</v>
+        <v>593</v>
       </c>
       <c r="G30" s="8">
         <f t="shared" si="0"/>
-        <v>3.6082474226804044E-2</v>
-      </c>
-      <c r="H30" s="7">
-        <f>AVERAGE(F28:F30)</f>
-        <v>570.12333333333333</v>
-      </c>
-      <c r="I30" s="14">
-        <f>AVERAGE(F26:F30)</f>
-        <v>574.06999999999994</v>
-      </c>
+        <v>-1.2440255133478819E-2</v>
+      </c>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
       <c r="J30" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>UP</v>
+        <v>DOWN</v>
       </c>
     </row>
     <row r="31" spans="1:16">
       <c r="A31" s="9">
+        <v>46181</v>
+      </c>
+      <c r="B31" s="9">
+        <v>46185</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E31" s="11">
+        <v>585.39</v>
+      </c>
+      <c r="F31" s="12">
+        <v>566.98</v>
+      </c>
+      <c r="G31" s="13">
+        <f t="shared" si="0"/>
+        <v>-3.1449119390491755E-2</v>
+      </c>
+      <c r="H31" s="10"/>
+      <c r="I31" s="10"/>
+      <c r="J31" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>DOWN</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32" s="4">
+        <v>46188</v>
+      </c>
+      <c r="B32" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E32" s="6">
+        <v>593.48</v>
+      </c>
+      <c r="F32" s="7">
+        <v>577.22</v>
+      </c>
+      <c r="G32" s="8">
+        <f t="shared" si="0"/>
+        <v>-2.7397721911437606E-2</v>
+      </c>
+      <c r="H32" s="7">
+        <f>AVERAGE(F30:F32)</f>
+        <v>579.06666666666672</v>
+      </c>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>DOWN</v>
+      </c>
+      <c r="P32" s="3"/>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="9">
+        <v>46195</v>
+      </c>
+      <c r="B33" s="9">
+        <v>46199</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E33" s="11">
+        <v>563.85</v>
+      </c>
+      <c r="F33" s="12">
+        <v>550.25</v>
+      </c>
+      <c r="G33" s="13">
+        <f t="shared" si="0"/>
+        <v>-2.4119890041677791E-2</v>
+      </c>
+      <c r="H33" s="12">
+        <f>AVERAGE(F31:F33)</f>
+        <v>564.81666666666672</v>
+      </c>
+      <c r="I33" s="10"/>
+      <c r="J33" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>DOWN</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="4">
+        <v>46202</v>
+      </c>
+      <c r="B34" s="4">
+        <v>46206</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E34" s="6">
+        <v>562.6</v>
+      </c>
+      <c r="F34" s="7">
+        <v>582.9</v>
+      </c>
+      <c r="G34" s="8">
+        <f t="shared" si="0"/>
+        <v>3.6082474226804044E-2</v>
+      </c>
+      <c r="H34" s="7">
+        <f>AVERAGE(F32:F34)</f>
+        <v>570.12333333333333</v>
+      </c>
+      <c r="I34" s="14">
+        <f>AVERAGE(F30:F34)</f>
+        <v>574.06999999999994</v>
+      </c>
+      <c r="J34" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>UP</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="9">
         <v>46209</v>
       </c>
-      <c r="B31" s="9">
+      <c r="B35" s="9">
+        <v>46213</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E35" s="12">
+        <v>583.5</v>
+      </c>
+      <c r="F35" s="12">
+        <v>590.20000000000005</v>
+      </c>
+      <c r="G35" s="13">
+        <f t="shared" si="0"/>
+        <v>1.1482433590402821E-2</v>
+      </c>
+      <c r="H35" s="12">
+        <f>AVERAGE(F33:F35)</f>
+        <v>574.45000000000005</v>
+      </c>
+      <c r="I35" s="15">
+        <f>AVERAGE(F31:F35)</f>
+        <v>573.51</v>
+      </c>
+      <c r="J35" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>UP</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="4">
         <v>46216</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="B36" s="4">
+        <v>46220</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D36" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D31" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E31" s="12">
-        <f>+F30</f>
-        <v>582.9</v>
-      </c>
-      <c r="F31" s="12">
-        <f>F30+AVERAGE(F27-F26,F28-F27,F29-F28)</f>
-        <v>568.65</v>
-      </c>
-      <c r="G31" s="13">
-        <f t="shared" si="0"/>
-        <v>-2.4446731857951622E-2</v>
-      </c>
-      <c r="H31" s="12">
-        <f>AVERAGE(F29:F31)</f>
-        <v>567.26666666666677</v>
-      </c>
-      <c r="I31" s="15">
-        <f>AVERAGE(F27:F31)</f>
-        <v>569.20000000000005</v>
-      </c>
-      <c r="J31" s="10" t="str">
+      <c r="E36" s="7">
+        <v>588</v>
+      </c>
+      <c r="F36" s="7">
+        <v>585.5</v>
+      </c>
+      <c r="G36" s="8">
+        <f t="shared" si="0"/>
+        <v>-4.2517006802721092E-3</v>
+      </c>
+      <c r="H36" s="7">
+        <f>AVERAGE(F34:F36)</f>
+        <v>586.19999999999993</v>
+      </c>
+      <c r="I36" s="14">
+        <f>AVERAGE(F32:F36)</f>
+        <v>577.21399999999994</v>
+      </c>
+      <c r="J36" s="5" t="str">
         <f t="shared" si="1"/>
         <v>DOWN</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="J1:J1048576">
+    <cfRule type="containsText" dxfId="14" priority="1" operator="containsText" text="up">
+      <formula>NOT(ISERROR(SEARCH("up",J1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="13" priority="2" operator="containsText" text="up">
+      <formula>NOT(ISERROR(SEARCH("up",J1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="12" priority="3" operator="containsText" text="down">
+      <formula>NOT(ISERROR(SEARCH("down",J1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
@@ -1613,31 +1882,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="E1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="F1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1648,7 +1917,7 @@
         <v>10</v>
       </c>
       <c r="C2" s="22" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D2">
         <v>390.49</v>
@@ -1668,7 +1937,7 @@
         <v>13</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D3">
         <v>308.63</v>
@@ -1688,7 +1957,7 @@
         <v>15</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D4">
         <v>194.83</v>
@@ -1705,10 +1974,10 @@
         <v>46209</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D5">
         <v>359.91</v>
@@ -1725,10 +1994,10 @@
         <v>46209</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D6">
         <v>582.9</v>
@@ -1744,13 +2013,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>